--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859D5F11-49BC-4A65-8C77-C2AE44502AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228B967C-D548-47FD-A83F-A240581C81AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 19-12-2025'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 29-01-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228B967C-D548-47FD-A83F-A240581C81AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E046AD4-DAF5-461E-BD52-202B8A60D3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 29-01-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-02-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E046AD4-DAF5-461E-BD52-202B8A60D3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8506D6A-92DC-41D0-96ED-4EF5E4DB3099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-02-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 20-02-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8506D6A-92DC-41D0-96ED-4EF5E4DB3099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7209F8E-DC6D-428B-803F-42F497F55E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 20-02-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 04-03-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7209F8E-DC6D-428B-803F-42F497F55E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6B73BC-C12F-4642-A733-5353F89BBEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 04-03-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 06-03-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6B73BC-C12F-4642-A733-5353F89BBEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51C738C-2850-49D3-B827-B331885FBC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51C738C-2850-49D3-B827-B331885FBC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D269B49-153C-411A-8635-2BD61105D5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D269B49-153C-411A-8635-2BD61105D5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9BB944-6FB2-451C-9530-DDD313FB7260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 06-03-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-03-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9BB944-6FB2-451C-9530-DDD313FB7260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1CC327-5C5D-4232-A930-4C85A282FCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1CC327-5C5D-4232-A930-4C85A282FCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA566CC0-49C5-4C3A-BB1F-D70450612874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-03-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 11-03-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA566CC0-49C5-4C3A-BB1F-D70450612874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95472410-8835-4E63-A674-0B4536BAD251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95472410-8835-4E63-A674-0B4536BAD251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239A6B28-20A6-4FA6-BAB5-CF333C8B3D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 11-03-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 20-03-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239A6B28-20A6-4FA6-BAB5-CF333C8B3D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F74D01A-1516-49C5-87A6-B2A24EE3D906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 20-03-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 25-03-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F74D01A-1516-49C5-87A6-B2A24EE3D906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBECD9B8-D698-4527-8AD9-346EA76692D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 25-03-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 08-04-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBECD9B8-D698-4527-8AD9-346EA76692D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FCE6C2-FF28-4D55-94E6-E40CF57084A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 08-04-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 10-04-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FCE6C2-FF28-4D55-94E6-E40CF57084A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC694C9-FF5E-4E77-9103-E2ED8B6444DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC694C9-FF5E-4E77-9103-E2ED8B6444DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104CC046-5442-4EB5-9EE4-D4086FA69517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 10-04-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 14-04-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104CC046-5442-4EB5-9EE4-D4086FA69517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EC555F-BCF5-4D4B-AAAB-A5A09166F462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 14-04-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 24-04-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EC555F-BCF5-4D4B-AAAB-A5A09166F462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759BFEF2-93A9-4DC5-A4E2-D7DE46AB26EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759BFEF2-93A9-4DC5-A4E2-D7DE46AB26EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360473BF-8E1A-4013-B095-B9E30CFF6ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 24-04-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 27-04-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360473BF-8E1A-4013-B095-B9E30CFF6ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CB379D-1B3D-4E53-A6E4-6E7AD53F9223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 27-04-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 06-05-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CB379D-1B3D-4E53-A6E4-6E7AD53F9223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB2B94E-669D-4611-AB47-5A6B530FC21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 06-05-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 01-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB2B94E-669D-4611-AB47-5A6B530FC21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66895262-69DE-4FC8-B572-34BD74B0D8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 01-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66895262-69DE-4FC8-B572-34BD74B0D8FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01CCC4F-FBDF-43BA-88EE-159ED50F5BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01CCC4F-FBDF-43BA-88EE-159ED50F5BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7513E93F-45B2-41FC-B07E-2E7D9968D654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 05-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228B967C-D548-47FD-A83F-A240581C81AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2FB7CC-5F9E-47D7-81CE-4CAC5FBB1FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1026A521-3280-4033-965A-85A05433B182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA52DAC-D988-47F1-B223-C0155372FDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA52DAC-D988-47F1-B223-C0155372FDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D9CFC6-4127-4A68-8EF4-0F1AF373A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D9CFC6-4127-4A68-8EF4-0F1AF373A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1E5CFE-5513-4F82-BC99-6B706F810BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 15-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1E5CFE-5513-4F82-BC99-6B706F810BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E73BC8A-F6A2-42F6-A48F-EC9A957AA7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 15-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 22-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E73BC8A-F6A2-42F6-A48F-EC9A957AA7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639F056B-7376-4879-9A1B-DC0A7E5528E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 22-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 23-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639F056B-7376-4879-9A1B-DC0A7E5528E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E188E2-F99D-4B5E-B703-A079939F5E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E73BC8A-F6A2-42F6-A48F-EC9A957AA7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557E5962-4E6C-4588-9746-A279FC39C58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 22-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 23-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557E5962-4E6C-4588-9746-A279FC39C58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1D10B9-700A-48AF-8472-A1166D40EFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 23-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 25-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1D10B9-700A-48AF-8472-A1166D40EFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357E3841-687F-4831-A01A-B0471D3932B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 25-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 30-06-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357E3841-687F-4831-A01A-B0471D3932B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCB9845-BE1E-438A-BBDC-47A928CA15BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCB9845-BE1E-438A-BBDC-47A928CA15BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD16A914-C6E5-45B0-9A46-848D95C21FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 30-06-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 01-07-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD16A914-C6E5-45B0-9A46-848D95C21FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AB816D-23DC-4C6B-B405-9F550CF4117D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 01-07-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-07-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD16A914-C6E5-45B0-9A46-848D95C21FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261ABE9B-1C6A-4790-983A-66C7C8E9E499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 01-07-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 03-07-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AB816D-23DC-4C6B-B405-9F550CF4117D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49029F1D-8CE0-4AFA-9ED6-6CF4C6B4C4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-07-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 03-07-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49029F1D-8CE0-4AFA-9ED6-6CF4C6B4C4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DF044D-C795-46B6-8C93-9C5A892556E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 03-07-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-07-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DF044D-C795-46B6-8C93-9C5A892556E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F405717-1F12-4006-A140-D0E65B3D8C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-07-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 19-08-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F405717-1F12-4006-A140-D0E65B3D8C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A19ED6-59EA-4C29-AB4F-40299F05BA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 19-08-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 21-08-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A19ED6-59EA-4C29-AB4F-40299F05BA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5F3DE8-67A5-49DE-BD02-2F62EA8601C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 21-08-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 27-08-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -547,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -567,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -587,7 +587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -601,7 +601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -615,7 +615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -635,7 +635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -655,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -689,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -760,7 +760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -797,7 +797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -851,7 +851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -879,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -896,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -916,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -930,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -947,7 +947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5F3DE8-67A5-49DE-BD02-2F62EA8601C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A6B274-BFBC-42E2-8F72-46E367B9D0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 27-08-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A6B274-BFBC-42E2-8F72-46E367B9D0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5AE1AB-9833-49E1-A026-D9416204878F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 02-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 06-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5AE1AB-9833-49E1-A026-D9416204878F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950A7639-E8EE-4833-A3D4-DB64A9AD7410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950A7639-E8EE-4833-A3D4-DB64A9AD7410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F20801A-1A05-4AF8-A010-72203CB2B27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 06-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 07-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F20801A-1A05-4AF8-A010-72203CB2B27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6C06E0-6264-4C8A-80C9-7FF7B1F65097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 07-09-2026'!$A$1:$F$28</definedName>
+    <definedName name="Sygehus_PAS_systemer">'Opdateret d. 09-09-2026'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Sygehus-PAS-systemer_excel.XLSX
+++ b/html/Sygehus-PAS-systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6C06E0-6264-4C8A-80C9-7FF7B1F65097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711EBC3D-9967-4529-8B8F-CC3EEA3784BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
